--- a/results/MC_Dist=Exp_n=300_LT=0.3_C=0.4_B=100.xlsx
+++ b/results/MC_Dist=Exp_n=300_LT=0.3_C=0.4_B=100.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -120,13 +120,16 @@
     <t xml:space="preserve">Gamma</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5,1</t>
+    <t xml:space="preserve">1,0.8</t>
   </si>
   <si>
     <t xml:space="preserve">x1.mean</t>
   </si>
   <si>
     <t xml:space="preserve">x1.sd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8</t>
   </si>
   <si>
     <t xml:space="preserve">x2.mean</t>
@@ -542,19 +545,19 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.08878600671627</v>
+        <v>-1.05235367209766</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0887860067162694</v>
+        <v>-0.0523536720976612</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0433320309168045</v>
+        <v>0.0427514592175873</v>
       </c>
       <c r="E2" t="n">
-        <v>0.189227765938842</v>
+        <v>0.201034074792696</v>
       </c>
       <c r="F2" t="n">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="G2" t="n">
         <v>0.98</v>
@@ -565,22 +568,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>-1.01008836263056</v>
+        <v>-0.993714502201212</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0100883626305615</v>
+        <v>0.00628549779878806</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0224016479458466</v>
+        <v>0.0256592092868769</v>
       </c>
       <c r="E3" t="n">
-        <v>0.150083723722949</v>
+        <v>0.160867916847979</v>
       </c>
       <c r="F3" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="4">
@@ -588,22 +591,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>1.56944634385756</v>
+        <v>1.0351928679369</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0694463438575617</v>
+        <v>0.0351928679368996</v>
       </c>
       <c r="D4" t="n">
-        <v>0.051290787117357</v>
+        <v>0.0365941440170824</v>
       </c>
       <c r="E4" t="n">
-        <v>0.216650331417255</v>
+        <v>0.188978129415636</v>
       </c>
       <c r="F4" t="n">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="G4" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="5">
@@ -611,19 +614,19 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>1.33180816235533</v>
+        <v>1.0151096152498</v>
       </c>
       <c r="C5" t="n">
-        <v>0.33180816235533</v>
+        <v>0.215109615249804</v>
       </c>
       <c r="D5" t="n">
-        <v>0.261709386857799</v>
+        <v>0.181823554035505</v>
       </c>
       <c r="E5" t="n">
-        <v>0.391336392342824</v>
+        <v>0.37002785516576</v>
       </c>
       <c r="F5" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="G5" t="n">
         <v>0.96</v>
@@ -634,19 +637,19 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>2.02454739877078</v>
+        <v>1.99329841793084</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0245473987707796</v>
+        <v>-0.00670158206916494</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00590813472011417</v>
+        <v>0.00638904452548236</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0732062254742335</v>
+        <v>0.0800513302702269</v>
       </c>
       <c r="F6" t="n">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="G6" t="n">
         <v>0.98</v>
@@ -780,20 +783,20 @@
         <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17" t="s">
         <v>7</v>
@@ -812,2325 +815,2325 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-1.29584229309698</v>
+        <v>-0.944603168880427</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.762295546143393</v>
+        <v>-0.898741956635994</v>
       </c>
       <c r="C2" t="n">
-        <v>1.10807491347963</v>
+        <v>0.933544135993715</v>
       </c>
       <c r="D2" t="n">
-        <v>1.74616464135564</v>
+        <v>0.761698376903272</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.07877129663765</v>
+        <v>-1.37939214313851</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.20990482213008</v>
+        <v>-1.43427435836282</v>
       </c>
       <c r="G2" t="n">
-        <v>2.07245298542768</v>
+        <v>2.2047678685269</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-1.16207282864374</v>
+        <v>-1.34315113064218</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.895184972847807</v>
+        <v>-0.781894331265228</v>
       </c>
       <c r="C3" t="n">
-        <v>1.36481523523594</v>
+        <v>0.748011111203724</v>
       </c>
       <c r="D3" t="n">
-        <v>1.48717230734904</v>
+        <v>1.5447976127674</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.98348028737656</v>
+        <v>-0.72357480849042</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.34176510750418</v>
+        <v>-1.70102260042645</v>
       </c>
       <c r="G3" t="n">
-        <v>2.11429960766973</v>
+        <v>2.10182348421335</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-0.98399771157359</v>
+        <v>-1.1354080061285</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.840581047200046</v>
+        <v>-0.937046189860948</v>
       </c>
       <c r="C4" t="n">
-        <v>1.44988638660772</v>
+        <v>1.01216281170394</v>
       </c>
       <c r="D4" t="n">
-        <v>0.941502496773108</v>
+        <v>0.797113369167488</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.13253394655959</v>
+        <v>-0.95294769869586</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.34887116261123</v>
+        <v>-1.68456568609217</v>
       </c>
       <c r="G4" t="n">
-        <v>2.17913837903905</v>
+        <v>2.08469296629498</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-1.17130787482877</v>
+        <v>-1.19389883535674</v>
       </c>
       <c r="B5" t="n">
-        <v>-1.08276199298862</v>
+        <v>-1.03189823394458</v>
       </c>
       <c r="C5" t="n">
-        <v>2.00213053157988</v>
+        <v>1.0265475766558</v>
       </c>
       <c r="D5" t="n">
-        <v>1.48940253604344</v>
+        <v>1.1936294293305</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.739767588171221</v>
+        <v>-1.07928932815199</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.20139907703368</v>
+        <v>-1.77742927006381</v>
       </c>
       <c r="G5" t="n">
-        <v>2.07145299183211</v>
+        <v>1.8610406117355</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0.834646993416597</v>
+        <v>-1.19358689262274</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.960411495405743</v>
+        <v>-1.05607449422321</v>
       </c>
       <c r="C6" t="n">
-        <v>1.54341522553646</v>
+        <v>1.226922224072</v>
       </c>
       <c r="D6" t="n">
-        <v>0.954761257411877</v>
+        <v>1.26019710473166</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.97533031549896</v>
+        <v>-0.819480646233941</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.64477595502453</v>
+        <v>-1.05737357031809</v>
       </c>
       <c r="G6" t="n">
-        <v>1.93165969250552</v>
+        <v>2.06598203995383</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-1.51895172766592</v>
+        <v>-1.30206982228906</v>
       </c>
       <c r="B7" t="n">
-        <v>-1.12321752368974</v>
+        <v>-1.07000375681673</v>
       </c>
       <c r="C7" t="n">
-        <v>1.97027263317699</v>
+        <v>1.072308856769</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1729570609972</v>
+        <v>1.35942911651454</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.695059148016752</v>
+        <v>-0.693942716279086</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.965788653188522</v>
+        <v>-1.18937763719416</v>
       </c>
       <c r="G7" t="n">
-        <v>1.98213745024339</v>
+        <v>1.95200017759558</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-0.922768305348312</v>
+        <v>-0.78100823754605</v>
       </c>
       <c r="B8" t="n">
-        <v>-1.007188807864</v>
+        <v>-1.1131959849715</v>
       </c>
       <c r="C8" t="n">
-        <v>1.45408306780621</v>
+        <v>1.18274833743871</v>
       </c>
       <c r="D8" t="n">
-        <v>1.41799991856296</v>
+        <v>0.77494524245538</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.51943987870459</v>
+        <v>-1.77403032519871</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.65898673726946</v>
+        <v>-1.77039759029482</v>
       </c>
       <c r="G8" t="n">
-        <v>2.08258237329729</v>
+        <v>2.11598537706968</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-1.16649660488646</v>
+        <v>-1.14404603253236</v>
       </c>
       <c r="B9" t="n">
-        <v>-1.18572928516906</v>
+        <v>-0.906752477158257</v>
       </c>
       <c r="C9" t="n">
-        <v>1.4732515000735</v>
+        <v>0.98028876390196</v>
       </c>
       <c r="D9" t="n">
-        <v>1.45908485659931</v>
+        <v>1.24282320762983</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.23162095972364</v>
+        <v>-1.13953293697946</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.10607865891173</v>
+        <v>-1.3504054130116</v>
       </c>
       <c r="G9" t="n">
-        <v>1.97162523525797</v>
+        <v>2.0093605156334</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-1.58410515505083</v>
+        <v>-1.02544364003973</v>
       </c>
       <c r="B10" t="n">
-        <v>-1.18045259508772</v>
+        <v>-1.33562113525269</v>
       </c>
       <c r="C10" t="n">
-        <v>1.8866901157856</v>
+        <v>1.3472297517729</v>
       </c>
       <c r="D10" t="n">
-        <v>2.107397116058</v>
+        <v>0.678397793970532</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.452756221228587</v>
+        <v>-0.984845702585378</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.52706672762799</v>
+        <v>-1.22082889636702</v>
       </c>
       <c r="G10" t="n">
-        <v>2.09107987104769</v>
+        <v>1.93465461364013</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-1.33249996568524</v>
+        <v>-0.817495528713505</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.948963708236273</v>
+        <v>-0.965264971107814</v>
       </c>
       <c r="C11" t="n">
-        <v>1.59173024124933</v>
+        <v>0.922501412238215</v>
       </c>
       <c r="D11" t="n">
-        <v>1.71923080480627</v>
+        <v>0.446668452423398</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.960420732888337</v>
+        <v>-1.36451494538813</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.06423221052395</v>
+        <v>-1.54514695116357</v>
       </c>
       <c r="G11" t="n">
-        <v>2.02408218475865</v>
+        <v>2.14781412119639</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-1.14955304351695</v>
+        <v>-1.02435388933752</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.972120241213506</v>
+        <v>-1.01354119867924</v>
       </c>
       <c r="C12" t="n">
-        <v>1.62786878142843</v>
+        <v>1.16468948648978</v>
       </c>
       <c r="D12" t="n">
-        <v>1.28428154658949</v>
+        <v>1.03081416087672</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.23746394749041</v>
+        <v>-1.34324707741121</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.91408178342984</v>
+        <v>-2.41578597459738</v>
       </c>
       <c r="G12" t="n">
-        <v>2.06859609402881</v>
+        <v>2.02880601742551</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-1.06491588828065</v>
+        <v>-0.827888284317971</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.914682810873376</v>
+        <v>-1.03340419600315</v>
       </c>
       <c r="C13" t="n">
-        <v>1.30114203379017</v>
+        <v>1.05436229871271</v>
       </c>
       <c r="D13" t="n">
-        <v>1.22916989716199</v>
+        <v>0.608586153646698</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.38824385697174</v>
+        <v>-1.85789913333343</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.41590232735531</v>
+        <v>-1.69155727507891</v>
       </c>
       <c r="G13" t="n">
-        <v>1.93411979935573</v>
+        <v>2.041646620511</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-0.835729539062472</v>
+        <v>-1.6368737988788</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.692756902809361</v>
+        <v>-0.930897895045878</v>
       </c>
       <c r="C14" t="n">
-        <v>1.25602682553901</v>
+        <v>1.0041431934894</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1455534137799</v>
+        <v>2.24783359753411</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.68434999943414</v>
+        <v>-0.493853568734477</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.78671631944401</v>
+        <v>-0.841134982103915</v>
       </c>
       <c r="G14" t="n">
-        <v>2.02119226502616</v>
+        <v>2.03803342821062</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-1.16501897793559</v>
+        <v>-0.657005508439359</v>
       </c>
       <c r="B15" t="n">
-        <v>-1.37577990488692</v>
+        <v>-0.880077077663495</v>
       </c>
       <c r="C15" t="n">
-        <v>2.10582345661278</v>
+        <v>0.986974897675879</v>
       </c>
       <c r="D15" t="n">
-        <v>1.55583869883921</v>
+        <v>0.426772905792638</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.883695704311122</v>
+        <v>-1.6396668458392</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.25727443211257</v>
+        <v>-1.95277884198427</v>
       </c>
       <c r="G15" t="n">
-        <v>2.03542214959676</v>
+        <v>2.02167707325784</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-1.18191774131327</v>
+        <v>-1.10910345187924</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.976667619987664</v>
+        <v>-0.67811293583803</v>
       </c>
       <c r="C16" t="n">
-        <v>1.61376829778353</v>
+        <v>0.774803037325043</v>
       </c>
       <c r="D16" t="n">
-        <v>1.36099129242208</v>
+        <v>1.33205771581497</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.712495622019254</v>
+        <v>-1.27635552998549</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.10248928578691</v>
+        <v>-1.33071647827376</v>
       </c>
       <c r="G16" t="n">
-        <v>2.05520399852325</v>
+        <v>1.90828955281845</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-0.69628063680197</v>
+        <v>-1.00560706438262</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.988517473146233</v>
+        <v>-1.01897511542186</v>
       </c>
       <c r="C17" t="n">
-        <v>1.61431079919481</v>
+        <v>1.06342006758221</v>
       </c>
       <c r="D17" t="n">
-        <v>0.879948927666306</v>
+        <v>0.950419184841481</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.94090870913575</v>
+        <v>-1.45783145876498</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.70840438686295</v>
+        <v>-1.54998673482357</v>
       </c>
       <c r="G17" t="n">
-        <v>2.04922213039283</v>
+        <v>1.99823399965475</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-0.99973033771056</v>
+        <v>-1.095484959228</v>
       </c>
       <c r="B18" t="n">
-        <v>-1.19288266060678</v>
+        <v>-0.794652006931777</v>
       </c>
       <c r="C18" t="n">
-        <v>1.58847494767019</v>
+        <v>0.77470720714262</v>
       </c>
       <c r="D18" t="n">
-        <v>1.33856942691292</v>
+        <v>1.15223341491665</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4540171230203</v>
+        <v>-1.39862334365877</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.65430243348815</v>
+        <v>-1.40960421365764</v>
       </c>
       <c r="G18" t="n">
-        <v>1.94756813724176</v>
+        <v>2.05902257094363</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-0.9629830745519</v>
+        <v>-1.21664259070486</v>
       </c>
       <c r="B19" t="n">
-        <v>-1.16993775379124</v>
+        <v>-1.13313033908158</v>
       </c>
       <c r="C19" t="n">
-        <v>1.8728267905858</v>
+        <v>1.00282140326593</v>
       </c>
       <c r="D19" t="n">
-        <v>1.00063811456321</v>
+        <v>1.32355357529794</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.15146241314183</v>
+        <v>-1.09652023847249</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.46989510599617</v>
+        <v>-1.13907194074013</v>
       </c>
       <c r="G19" t="n">
-        <v>2.18981778370335</v>
+        <v>1.99059538981473</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-1.07956517961095</v>
+        <v>-0.934369400934864</v>
       </c>
       <c r="B20" t="n">
-        <v>-1.31413822605271</v>
+        <v>-0.965729630178696</v>
       </c>
       <c r="C20" t="n">
-        <v>1.95020587506135</v>
+        <v>1.00445389709874</v>
       </c>
       <c r="D20" t="n">
-        <v>1.46990985408712</v>
+        <v>0.456354991621314</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.40883396619724</v>
+        <v>-2.00148895162961</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.46056032227182</v>
+        <v>-1.4459105497078</v>
       </c>
       <c r="G20" t="n">
-        <v>1.95954030848234</v>
+        <v>1.91982693474381</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-1.20229436395536</v>
+        <v>-0.830318529476929</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.753543460170251</v>
+        <v>-1.18151838643901</v>
       </c>
       <c r="C21" t="n">
-        <v>1.36639352555894</v>
+        <v>1.22409981738216</v>
       </c>
       <c r="D21" t="n">
-        <v>1.56799159692456</v>
+        <v>0.710718276698579</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.35938597404375</v>
+        <v>-1.5126715998131</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5061097218848</v>
+        <v>-1.72289350248295</v>
       </c>
       <c r="G21" t="n">
-        <v>1.8806647472264</v>
+        <v>1.98185344489869</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>-1.07365970703515</v>
+        <v>-0.832522951824408</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.830548417690458</v>
+        <v>-0.940081613641005</v>
       </c>
       <c r="C22" t="n">
-        <v>1.46876337147959</v>
+        <v>1.05526035185208</v>
       </c>
       <c r="D22" t="n">
-        <v>1.50443586791574</v>
+        <v>0.401018167876482</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.23808350650649</v>
+        <v>-1.29112523350833</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.31007098128525</v>
+        <v>-1.52609831595965</v>
       </c>
       <c r="G22" t="n">
-        <v>2.04773304990367</v>
+        <v>2.10015401079485</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-1.26353009226401</v>
+        <v>-0.917868391963007</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.908223017070469</v>
+        <v>-1.19443597184716</v>
       </c>
       <c r="C23" t="n">
-        <v>1.3386967829231</v>
+        <v>1.17322725798555</v>
       </c>
       <c r="D23" t="n">
-        <v>1.69831193439001</v>
+        <v>1.07506573207901</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.03185684996075</v>
+        <v>-1.59852071061554</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.05584429240627</v>
+        <v>-2.60838478395394</v>
       </c>
       <c r="G23" t="n">
-        <v>2.04015670870873</v>
+        <v>1.91902717984695</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>-0.925537238603387</v>
+        <v>-1.04143927427009</v>
       </c>
       <c r="B24" t="n">
-        <v>-1.01734153963783</v>
+        <v>-1.21836982759547</v>
       </c>
       <c r="C24" t="n">
-        <v>1.60852968284527</v>
+        <v>1.15050126440694</v>
       </c>
       <c r="D24" t="n">
-        <v>0.938515738583495</v>
+        <v>0.824698640998304</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.46709176297154</v>
+        <v>-1.2377709338148</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4435335559219</v>
+        <v>-1.40844985529777</v>
       </c>
       <c r="G24" t="n">
-        <v>2.14241688910429</v>
+        <v>1.93453103055619</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>-1.09483603234389</v>
+        <v>-1.13420618664636</v>
       </c>
       <c r="B25" t="n">
-        <v>-1.07795383816042</v>
+        <v>-0.860750280223419</v>
       </c>
       <c r="C25" t="n">
-        <v>1.62742536331351</v>
+        <v>0.697027003692473</v>
       </c>
       <c r="D25" t="n">
-        <v>1.4002131252788</v>
+        <v>1.00460475986969</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.1746039574181</v>
+        <v>-1.24986568006034</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.16581383108756</v>
+        <v>-1.42960904541353</v>
       </c>
       <c r="G25" t="n">
-        <v>2.02170987290773</v>
+        <v>1.81826637081548</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>-1.18674656693599</v>
+        <v>-1.06430674873441</v>
       </c>
       <c r="B26" t="n">
-        <v>-1.24375353613833</v>
+        <v>-0.941083500936193</v>
       </c>
       <c r="C26" t="n">
-        <v>1.82630238141986</v>
+        <v>0.983999185604342</v>
       </c>
       <c r="D26" t="n">
-        <v>1.88969560192308</v>
+        <v>1.16706268825293</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.43563453746974</v>
+        <v>-1.34280271505065</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.48239472701031</v>
+        <v>-1.51930406790959</v>
       </c>
       <c r="G26" t="n">
-        <v>1.95708755270093</v>
+        <v>1.94748247481931</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>-1.15523275378743</v>
+        <v>-1.01718390459475</v>
       </c>
       <c r="B27" t="n">
-        <v>-0.949830237735136</v>
+        <v>-0.991607333118621</v>
       </c>
       <c r="C27" t="n">
-        <v>1.53571858887664</v>
+        <v>1.00700269967249</v>
       </c>
       <c r="D27" t="n">
-        <v>1.5448686122362</v>
+        <v>0.927175604170673</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.16259693177385</v>
+        <v>-1.37797294011626</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.41074791693648</v>
+        <v>-1.39896411731835</v>
       </c>
       <c r="G27" t="n">
-        <v>2.00336472055164</v>
+        <v>1.99180488552848</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>-1.23125035778689</v>
+        <v>-1.11987792721973</v>
       </c>
       <c r="B28" t="n">
-        <v>-0.916422563237635</v>
+        <v>-1.04480381321121</v>
       </c>
       <c r="C28" t="n">
-        <v>1.50838190278893</v>
+        <v>1.01739265814006</v>
       </c>
       <c r="D28" t="n">
-        <v>1.72439339942673</v>
+        <v>1.11672920601569</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.07926388583922</v>
+        <v>-1.31882864455669</v>
       </c>
       <c r="F28" t="n">
-        <v>-2.27952688811584</v>
+        <v>-1.32089454185577</v>
       </c>
       <c r="G28" t="n">
-        <v>1.96991008818795</v>
+        <v>2.03630201805412</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>-0.858899358573005</v>
+        <v>-1.17315990926224</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.929066399115906</v>
+        <v>-0.860226129727466</v>
       </c>
       <c r="C29" t="n">
-        <v>1.33436759544287</v>
+        <v>0.976955967847313</v>
       </c>
       <c r="D29" t="n">
-        <v>1.14474122757813</v>
+        <v>1.26163392102996</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.75769857666644</v>
+        <v>-1.04170463046317</v>
       </c>
       <c r="F29" t="n">
-        <v>-2.62196288285261</v>
+        <v>-1.32875101039902</v>
       </c>
       <c r="G29" t="n">
-        <v>1.98770216601589</v>
+        <v>2.055090619068</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>-0.912067892976652</v>
+        <v>-1.24716940043379</v>
       </c>
       <c r="B30" t="n">
-        <v>-1.03402541409473</v>
+        <v>-1.17673772879421</v>
       </c>
       <c r="C30" t="n">
-        <v>1.46859940997766</v>
+        <v>1.15565717391082</v>
       </c>
       <c r="D30" t="n">
-        <v>1.09634841899079</v>
+        <v>1.27590579960161</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.64693133359492</v>
+        <v>-1.11181217847223</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.65381434333773</v>
+        <v>-1.2008357668222</v>
       </c>
       <c r="G30" t="n">
-        <v>1.90727397475823</v>
+        <v>1.97871514772015</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>-0.900576074999886</v>
+        <v>-0.937446908305824</v>
       </c>
       <c r="B31" t="n">
-        <v>-1.00306134861234</v>
+        <v>-0.884267626170046</v>
       </c>
       <c r="C31" t="n">
-        <v>1.33053573087513</v>
+        <v>1.04557902727287</v>
       </c>
       <c r="D31" t="n">
-        <v>1.15658571024391</v>
+        <v>0.604808877837725</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.74700031290633</v>
+        <v>-1.52495816510802</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.72559349827465</v>
+        <v>-1.47286333484379</v>
       </c>
       <c r="G31" t="n">
-        <v>1.90778525017378</v>
+        <v>1.96990840094501</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>-1.13376399875555</v>
+        <v>-0.910927142147981</v>
       </c>
       <c r="B32" t="n">
-        <v>-1.2140271035297</v>
+        <v>-1.01928767234476</v>
       </c>
       <c r="C32" t="n">
-        <v>1.84857905936067</v>
+        <v>0.931834744430809</v>
       </c>
       <c r="D32" t="n">
-        <v>1.35576124360536</v>
+        <v>0.70234315003854</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.069697375199</v>
+        <v>-1.65907081143476</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.98427285230445</v>
+        <v>-1.56157564698932</v>
       </c>
       <c r="G32" t="n">
-        <v>2.11505576275213</v>
+        <v>1.98635849172021</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>-0.978579705214379</v>
+        <v>-1.01873607968269</v>
       </c>
       <c r="B33" t="n">
-        <v>-1.07266605930328</v>
+        <v>-0.997815842366875</v>
       </c>
       <c r="C33" t="n">
-        <v>1.55432644541839</v>
+        <v>1.24531559048592</v>
       </c>
       <c r="D33" t="n">
-        <v>1.10998753695715</v>
+        <v>0.610243592351683</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.26104712737166</v>
+        <v>-1.6460131345206</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.48241304433694</v>
+        <v>-1.26401444815053</v>
       </c>
       <c r="G33" t="n">
-        <v>2.01001810295215</v>
+        <v>1.96660159572036</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>-1.39814582171739</v>
+        <v>-1.23816605690309</v>
       </c>
       <c r="B34" t="n">
-        <v>-0.876563758111591</v>
+        <v>-1.16648777447102</v>
       </c>
       <c r="C34" t="n">
-        <v>1.38583965015165</v>
+        <v>1.38256909880369</v>
       </c>
       <c r="D34" t="n">
-        <v>1.76757128923896</v>
+        <v>1.34067990329435</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.15320584927252</v>
+        <v>-0.898682982550097</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.02926419989722</v>
+        <v>-1.90993445512528</v>
       </c>
       <c r="G34" t="n">
-        <v>2.01808229246571</v>
+        <v>2.10962668735557</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>-0.94519875527716</v>
+        <v>-0.973949911991326</v>
       </c>
       <c r="B35" t="n">
-        <v>-1.01142450934247</v>
+        <v>-0.865823204857685</v>
       </c>
       <c r="C35" t="n">
-        <v>1.44585362841185</v>
+        <v>0.701463532534997</v>
       </c>
       <c r="D35" t="n">
-        <v>0.950993086143691</v>
+        <v>0.798694069170592</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.907965218984788</v>
+        <v>-1.42805513566008</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.44192598919153</v>
+        <v>-2.41781820585318</v>
       </c>
       <c r="G35" t="n">
-        <v>1.94690701302337</v>
+        <v>1.97565363099944</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>-1.12325101270224</v>
+        <v>-1.19825294372012</v>
       </c>
       <c r="B36" t="n">
-        <v>-0.918737081467176</v>
+        <v>-0.915232082095846</v>
       </c>
       <c r="C36" t="n">
-        <v>1.46582098808481</v>
+        <v>0.889987844477238</v>
       </c>
       <c r="D36" t="n">
-        <v>1.33857282972786</v>
+        <v>1.32761076349783</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.00429099607631</v>
+        <v>-1.45796555162294</v>
       </c>
       <c r="F36" t="n">
-        <v>-2.13389848997971</v>
+        <v>-1.26359528695501</v>
       </c>
       <c r="G36" t="n">
-        <v>2.15208225153463</v>
+        <v>2.01548176766436</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>-1.04738678122245</v>
+        <v>-0.985439553065923</v>
       </c>
       <c r="B37" t="n">
-        <v>-0.866193043491137</v>
+        <v>-1.23626743005315</v>
       </c>
       <c r="C37" t="n">
-        <v>1.46304368516656</v>
+        <v>1.26357567645178</v>
       </c>
       <c r="D37" t="n">
-        <v>1.25444294518312</v>
+        <v>0.814147519161349</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.17735435403295</v>
+        <v>-1.26989275431598</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.58267881728734</v>
+        <v>-1.43352837293258</v>
       </c>
       <c r="G37" t="n">
-        <v>2.05478899778732</v>
+        <v>1.97297385724416</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>-1.3174251455951</v>
+        <v>-0.694572894259809</v>
       </c>
       <c r="B38" t="n">
-        <v>-0.895313127439828</v>
+        <v>-1.09858820264851</v>
       </c>
       <c r="C38" t="n">
-        <v>1.38820927664342</v>
+        <v>1.26639826341081</v>
       </c>
       <c r="D38" t="n">
-        <v>1.8511847962354</v>
+        <v>0.614056660815865</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.546356677778693</v>
+        <v>-1.869067819895</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.930357908753272</v>
+        <v>-2.72134032876305</v>
       </c>
       <c r="G38" t="n">
-        <v>2.12110429029717</v>
+        <v>1.91760879597592</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>-1.07168512204479</v>
+        <v>-1.2930237227833</v>
       </c>
       <c r="B39" t="n">
-        <v>-0.805655601936194</v>
+        <v>-1.2924810087944</v>
       </c>
       <c r="C39" t="n">
-        <v>1.08352295029358</v>
+        <v>1.46217379636775</v>
       </c>
       <c r="D39" t="n">
-        <v>1.42492059035259</v>
+        <v>0.968489716171083</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.21263841568299</v>
+        <v>-0.53572820029216</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.19714266972041</v>
+        <v>-1.52165616825428</v>
       </c>
       <c r="G39" t="n">
-        <v>2.06250545722318</v>
+        <v>1.99090833400914</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>-1.193213143578</v>
+        <v>-0.779863585328855</v>
       </c>
       <c r="B40" t="n">
-        <v>-1.06401799309075</v>
+        <v>-0.930127915097017</v>
       </c>
       <c r="C40" t="n">
-        <v>1.58012788034921</v>
+        <v>0.934895725173345</v>
       </c>
       <c r="D40" t="n">
-        <v>1.11650377160523</v>
+        <v>0.798102236960599</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.07841146964623</v>
+        <v>-1.82521910566743</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.14326408335504</v>
+        <v>-1.96111601053821</v>
       </c>
       <c r="G40" t="n">
-        <v>2.00898395389</v>
+        <v>2.02961728372333</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>-1.27070140725229</v>
+        <v>-1.08897031058784</v>
       </c>
       <c r="B41" t="n">
-        <v>-0.996252680341683</v>
+        <v>-0.9173624256066</v>
       </c>
       <c r="C41" t="n">
-        <v>1.47200832125011</v>
+        <v>0.868271808871344</v>
       </c>
       <c r="D41" t="n">
-        <v>1.44510753581173</v>
+        <v>1.12843147680147</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.89604475911502</v>
+        <v>-1.23578434895866</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.87196636806644</v>
+        <v>-1.41796176051128</v>
       </c>
       <c r="G41" t="n">
-        <v>2.05968565492991</v>
+        <v>1.89861595945437</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>-1.05515353586464</v>
+        <v>-0.801425961690233</v>
       </c>
       <c r="B42" t="n">
-        <v>-0.844866422103584</v>
+        <v>-1.30072904710687</v>
       </c>
       <c r="C42" t="n">
-        <v>1.33101241247855</v>
+        <v>1.19076098137639</v>
       </c>
       <c r="D42" t="n">
-        <v>1.34174943551522</v>
+        <v>0.869337214959699</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.25468843912703</v>
+        <v>-1.6721806118053</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.50563381511002</v>
+        <v>-1.98158346603433</v>
       </c>
       <c r="G42" t="n">
-        <v>1.93156103533207</v>
+        <v>1.8544565755132</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>-0.964547010624206</v>
+        <v>-1.42909555348605</v>
       </c>
       <c r="B43" t="n">
-        <v>-1.04558980299147</v>
+        <v>-1.00022064559847</v>
       </c>
       <c r="C43" t="n">
-        <v>1.49141419901158</v>
+        <v>0.95664438857148</v>
       </c>
       <c r="D43" t="n">
-        <v>0.906857311743795</v>
+        <v>1.72602664910765</v>
       </c>
       <c r="E43" t="n">
-        <v>-1.19836306093925</v>
+        <v>-0.783973665065124</v>
       </c>
       <c r="F43" t="n">
-        <v>-1.35408196483591</v>
+        <v>-1.00826386781282</v>
       </c>
       <c r="G43" t="n">
-        <v>2.05711974123712</v>
+        <v>1.94214042684521</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>-1.20271059576351</v>
+        <v>-1.11025458884321</v>
       </c>
       <c r="B44" t="n">
-        <v>-0.92863250982281</v>
+        <v>-0.870376890850626</v>
       </c>
       <c r="C44" t="n">
-        <v>1.49557355332704</v>
+        <v>1.07513751198436</v>
       </c>
       <c r="D44" t="n">
-        <v>1.39424062110604</v>
+        <v>1.11395905095721</v>
       </c>
       <c r="E44" t="n">
-        <v>-1.02572799655479</v>
+        <v>-1.0858221020437</v>
       </c>
       <c r="F44" t="n">
-        <v>-2.03150765573684</v>
+        <v>-2.13107540537152</v>
       </c>
       <c r="G44" t="n">
-        <v>2.03680264328352</v>
+        <v>2.10328954343599</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>-0.849910686995733</v>
+        <v>-1.19567004408425</v>
       </c>
       <c r="B45" t="n">
-        <v>-1.01259412074651</v>
+        <v>-1.08866368982073</v>
       </c>
       <c r="C45" t="n">
-        <v>1.6464934768693</v>
+        <v>1.15831807556798</v>
       </c>
       <c r="D45" t="n">
-        <v>0.51202995051774</v>
+        <v>1.20323998302685</v>
       </c>
       <c r="E45" t="n">
-        <v>-1.2292213644768</v>
+        <v>-1.19494305201716</v>
       </c>
       <c r="F45" t="n">
-        <v>-2.22504741442271</v>
+        <v>-1.23868778807891</v>
       </c>
       <c r="G45" t="n">
-        <v>2.1056133342067</v>
+        <v>1.940860324659</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>-1.06490851176256</v>
+        <v>-1.11302559413377</v>
       </c>
       <c r="B46" t="n">
-        <v>-1.27753484556478</v>
+        <v>-1.1042635159926</v>
       </c>
       <c r="C46" t="n">
-        <v>2.09155181853235</v>
+        <v>0.930284582706545</v>
       </c>
       <c r="D46" t="n">
-        <v>1.40835168834366</v>
+        <v>1.02604089524384</v>
       </c>
       <c r="E46" t="n">
-        <v>-1.28806937337615</v>
+        <v>-1.20863614954074</v>
       </c>
       <c r="F46" t="n">
-        <v>-1.57984629953711</v>
+        <v>-2.19368194494359</v>
       </c>
       <c r="G46" t="n">
-        <v>1.94486915643577</v>
+        <v>1.93047286629397</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>-1.20871731605412</v>
+        <v>-0.96605122902897</v>
       </c>
       <c r="B47" t="n">
-        <v>-1.04824060448504</v>
+        <v>-0.835238349695713</v>
       </c>
       <c r="C47" t="n">
-        <v>1.5470318052027</v>
+        <v>0.726290642639437</v>
       </c>
       <c r="D47" t="n">
-        <v>1.69434487497053</v>
+        <v>1.00496907817043</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.672030013883432</v>
+        <v>-1.48949946804347</v>
       </c>
       <c r="F47" t="n">
-        <v>-1.25652530464959</v>
+        <v>-1.54108705732308</v>
       </c>
       <c r="G47" t="n">
-        <v>2.05059640789824</v>
+        <v>2.01653406756272</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>-1.07493480085463</v>
+        <v>-1.01562458258986</v>
       </c>
       <c r="B48" t="n">
-        <v>-0.924188524022738</v>
+        <v>-0.985450991117574</v>
       </c>
       <c r="C48" t="n">
-        <v>1.34994199924017</v>
+        <v>1.09208138748937</v>
       </c>
       <c r="D48" t="n">
-        <v>1.56413415762067</v>
+        <v>1.03927805070838</v>
       </c>
       <c r="E48" t="n">
-        <v>-1.32743822136053</v>
+        <v>-1.76530873038109</v>
       </c>
       <c r="F48" t="n">
-        <v>-1.53148821101569</v>
+        <v>-1.51241502399535</v>
       </c>
       <c r="G48" t="n">
-        <v>2.04297506548773</v>
+        <v>1.99564606629225</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>-1.31647355106159</v>
+        <v>-1.11182277083008</v>
       </c>
       <c r="B49" t="n">
-        <v>-0.920503642377446</v>
+        <v>-0.850818904962152</v>
       </c>
       <c r="C49" t="n">
-        <v>1.61757987744772</v>
+        <v>1.13579526701492</v>
       </c>
       <c r="D49" t="n">
-        <v>1.96787407820144</v>
+        <v>1.02199559319082</v>
       </c>
       <c r="E49" t="n">
-        <v>-1.0860839847343</v>
+        <v>-1.35166812388962</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.98594006352995</v>
+        <v>-2.44951488607116</v>
       </c>
       <c r="G49" t="n">
-        <v>2.07175255031178</v>
+        <v>1.97380791605701</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>-0.908603890358718</v>
+        <v>-0.919761993817845</v>
       </c>
       <c r="B50" t="n">
-        <v>-0.693707138623531</v>
+        <v>-0.982061901358306</v>
       </c>
       <c r="C50" t="n">
-        <v>1.30377277107195</v>
+        <v>1.17987368617038</v>
       </c>
       <c r="D50" t="n">
-        <v>1.27927440294244</v>
+        <v>0.90479694521536</v>
       </c>
       <c r="E50" t="n">
-        <v>-1.5136305143015</v>
+        <v>-1.48017604043488</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.67289017915621</v>
+        <v>-1.42797572758654</v>
       </c>
       <c r="G50" t="n">
-        <v>2.07469976253436</v>
+        <v>2.12346061454701</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>-1.01087952099637</v>
+        <v>-1.28334580043828</v>
       </c>
       <c r="B51" t="n">
-        <v>-1.2430074887732</v>
+        <v>-1.01305395565601</v>
       </c>
       <c r="C51" t="n">
-        <v>1.68087763159979</v>
+        <v>0.9849971141119</v>
       </c>
       <c r="D51" t="n">
-        <v>1.06847768580466</v>
+        <v>1.31768460592762</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.35270603465869</v>
+        <v>-1.1198113639105</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.56435937712367</v>
+        <v>-1.03374853819393</v>
       </c>
       <c r="G51" t="n">
-        <v>1.82560515524189</v>
+        <v>2.02160761123599</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>-0.898618226159914</v>
+        <v>-1.0402311685035</v>
       </c>
       <c r="B52" t="n">
-        <v>-0.965711162287497</v>
+        <v>-0.932943244516237</v>
       </c>
       <c r="C52" t="n">
-        <v>1.45809518771136</v>
+        <v>1.30728038466111</v>
       </c>
       <c r="D52" t="n">
-        <v>0.760636644015977</v>
+        <v>1.02198421778933</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.28062550764402</v>
+        <v>-1.32702831108426</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.60855227150181</v>
+        <v>-2.03665261686308</v>
       </c>
       <c r="G52" t="n">
-        <v>1.93408247087842</v>
+        <v>2.01790312784077</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>-0.820579189228095</v>
+        <v>-0.625555088355856</v>
       </c>
       <c r="B53" t="n">
-        <v>-1.04625631707222</v>
+        <v>-0.74820303095608</v>
       </c>
       <c r="C53" t="n">
-        <v>1.71212699225112</v>
+        <v>0.805622394546684</v>
       </c>
       <c r="D53" t="n">
-        <v>0.632932921194122</v>
+        <v>0.272463177781172</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.397771876682</v>
+        <v>-1.61523876646832</v>
       </c>
       <c r="F53" t="n">
-        <v>-2.52030392880904</v>
+        <v>-1.92867215678371</v>
       </c>
       <c r="G53" t="n">
-        <v>2.18456555120607</v>
+        <v>2.2111814400526</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>-1.11207663826638</v>
+        <v>-1.00057392457671</v>
       </c>
       <c r="B54" t="n">
-        <v>-0.835045233288802</v>
+        <v>-0.998670866566305</v>
       </c>
       <c r="C54" t="n">
-        <v>1.41547905121632</v>
+        <v>0.984081750979977</v>
       </c>
       <c r="D54" t="n">
-        <v>1.41469747521784</v>
+        <v>0.97490298784888</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.13169863303954</v>
+        <v>-1.18479203886253</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.94640902604769</v>
+        <v>-1.49962074070558</v>
       </c>
       <c r="G54" t="n">
-        <v>1.98963222595428</v>
+        <v>1.9411908818082</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>-1.21432213105667</v>
+        <v>-1.25908197042909</v>
       </c>
       <c r="B55" t="n">
-        <v>-0.971649225997769</v>
+        <v>-1.17754273519373</v>
       </c>
       <c r="C55" t="n">
-        <v>1.44639966077211</v>
+        <v>1.2978158237608</v>
       </c>
       <c r="D55" t="n">
-        <v>1.49882777607375</v>
+        <v>1.63057913131721</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.648449727428678</v>
+        <v>-1.07388802307919</v>
       </c>
       <c r="F55" t="n">
-        <v>-1.29115226002259</v>
+        <v>-1.16754963406086</v>
       </c>
       <c r="G55" t="n">
-        <v>1.94151162171013</v>
+        <v>2.08847509513889</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>-0.868778712168963</v>
+        <v>-1.04048005597179</v>
       </c>
       <c r="B56" t="n">
-        <v>-1.08474142920766</v>
+        <v>-0.973447472935995</v>
       </c>
       <c r="C56" t="n">
-        <v>1.84797245402763</v>
+        <v>0.905587205615292</v>
       </c>
       <c r="D56" t="n">
-        <v>0.800611582899709</v>
+        <v>1.1998076397208</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.33128777683629</v>
+        <v>-1.2777688530641</v>
       </c>
       <c r="F56" t="n">
-        <v>-2.34037232938985</v>
+        <v>-1.42459075658497</v>
       </c>
       <c r="G56" t="n">
-        <v>2.08393888368181</v>
+        <v>2.01541205723361</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>-0.967867832627703</v>
+        <v>-1.22685484810436</v>
       </c>
       <c r="B57" t="n">
-        <v>-0.886484603669397</v>
+        <v>-1.03275439024982</v>
       </c>
       <c r="C57" t="n">
-        <v>1.37975557800714</v>
+        <v>1.08627785649426</v>
       </c>
       <c r="D57" t="n">
-        <v>0.946617264119538</v>
+        <v>1.2793572461137</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.24757159361207</v>
+        <v>-1.03875092650344</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.37638546451033</v>
+        <v>-1.32255726445236</v>
       </c>
       <c r="G57" t="n">
-        <v>2.13813686118309</v>
+        <v>1.9813513186971</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>-0.95686532461103</v>
+        <v>-0.925460360800422</v>
       </c>
       <c r="B58" t="n">
-        <v>-0.92434879932128</v>
+        <v>-1.04499226556828</v>
       </c>
       <c r="C58" t="n">
-        <v>1.4631574073808</v>
+        <v>1.00003476328116</v>
       </c>
       <c r="D58" t="n">
-        <v>0.869401162638656</v>
+        <v>0.588548604018162</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.32578257565447</v>
+        <v>-1.61784364717939</v>
       </c>
       <c r="F58" t="n">
-        <v>-2.51402123553695</v>
+        <v>-1.52298077172078</v>
       </c>
       <c r="G58" t="n">
-        <v>2.15384084089468</v>
+        <v>1.8613981858431</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>-1.08435936918258</v>
+        <v>-0.780299707480063</v>
       </c>
       <c r="B59" t="n">
-        <v>-1.03058499353149</v>
+        <v>-1.23988838472382</v>
       </c>
       <c r="C59" t="n">
-        <v>1.83256880611412</v>
+        <v>1.31831279348228</v>
       </c>
       <c r="D59" t="n">
-        <v>1.244257301289</v>
+        <v>0.85022655750455</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.0721104361875</v>
+        <v>-1.73042426757935</v>
       </c>
       <c r="F59" t="n">
-        <v>-2.14489238517222</v>
+        <v>-2.5272174756828</v>
       </c>
       <c r="G59" t="n">
-        <v>2.06868880052934</v>
+        <v>2.03842785684419</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>-0.83014129375818</v>
+        <v>-0.89397590208306</v>
       </c>
       <c r="B60" t="n">
-        <v>-1.04039468699245</v>
+        <v>-0.984625466588296</v>
       </c>
       <c r="C60" t="n">
-        <v>1.74761458245759</v>
+        <v>1.14783638564237</v>
       </c>
       <c r="D60" t="n">
-        <v>0.593755031260101</v>
+        <v>0.681190974741847</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.44947343289288</v>
+        <v>-1.43332178274153</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.53505477598851</v>
+        <v>-1.41115919015945</v>
       </c>
       <c r="G60" t="n">
-        <v>2.06300144082184</v>
+        <v>1.98899284251944</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>-1.27550601698451</v>
+        <v>-1.17034663619067</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.974833617253093</v>
+        <v>-0.737559343803397</v>
       </c>
       <c r="C61" t="n">
-        <v>1.52423602380651</v>
+        <v>0.754940806158935</v>
       </c>
       <c r="D61" t="n">
-        <v>1.72017063442152</v>
+        <v>1.25687058527973</v>
       </c>
       <c r="E61" t="n">
-        <v>-1.00182659670315</v>
+        <v>-1.05902479484595</v>
       </c>
       <c r="F61" t="n">
-        <v>-2.21799527961261</v>
+        <v>-1.3812070432475</v>
       </c>
       <c r="G61" t="n">
-        <v>2.0965265909791</v>
+        <v>1.87797994881732</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>-1.11217008687787</v>
+        <v>-0.852447141212849</v>
       </c>
       <c r="B62" t="n">
-        <v>-1.0923016653566</v>
+        <v>-0.85890924588941</v>
       </c>
       <c r="C62" t="n">
-        <v>1.7587755126382</v>
+        <v>1.10437742438586</v>
       </c>
       <c r="D62" t="n">
-        <v>1.3530161669253</v>
+        <v>0.619041882067112</v>
       </c>
       <c r="E62" t="n">
-        <v>-1.7658475033178</v>
+        <v>-1.42200047069349</v>
       </c>
       <c r="F62" t="n">
-        <v>-1.39212789311036</v>
+        <v>-2.57325674519087</v>
       </c>
       <c r="G62" t="n">
-        <v>1.97204203440418</v>
+        <v>2.02189198075087</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>-1.06221290506282</v>
+        <v>-1.02921556094752</v>
       </c>
       <c r="B63" t="n">
-        <v>-1.05302618805946</v>
+        <v>-0.955808904688674</v>
       </c>
       <c r="C63" t="n">
-        <v>1.53234355211926</v>
+        <v>0.958799377560263</v>
       </c>
       <c r="D63" t="n">
-        <v>1.40453479140569</v>
+        <v>1.12714897985702</v>
       </c>
       <c r="E63" t="n">
-        <v>-1.21252601162549</v>
+        <v>-1.50723789267593</v>
       </c>
       <c r="F63" t="n">
-        <v>-1.44488962922347</v>
+        <v>-1.60813737354026</v>
       </c>
       <c r="G63" t="n">
-        <v>1.94839832340045</v>
+        <v>1.99153497308905</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>-1.05076859899123</v>
+        <v>-1.07610660450175</v>
       </c>
       <c r="B64" t="n">
-        <v>-1.0314617050318</v>
+        <v>-1.03305364558298</v>
       </c>
       <c r="C64" t="n">
-        <v>1.4758525017714</v>
+        <v>1.02945963032596</v>
       </c>
       <c r="D64" t="n">
-        <v>1.15217857876677</v>
+        <v>0.906430227862781</v>
       </c>
       <c r="E64" t="n">
-        <v>-1.36249733098</v>
+        <v>-1.19550447939555</v>
       </c>
       <c r="F64" t="n">
-        <v>-2.36027282129375</v>
+        <v>-1.30725921722152</v>
       </c>
       <c r="G64" t="n">
-        <v>1.98864768645433</v>
+        <v>1.93474599259887</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>-0.87270086436412</v>
+        <v>-0.616088499661334</v>
       </c>
       <c r="B65" t="n">
-        <v>-1.2093495236144</v>
+        <v>-1.07558440147717</v>
       </c>
       <c r="C65" t="n">
-        <v>1.83963826241486</v>
+        <v>1.07874267739728</v>
       </c>
       <c r="D65" t="n">
-        <v>0.951928431413001</v>
+        <v>0.505809727133266</v>
       </c>
       <c r="E65" t="n">
-        <v>-1.53780321671024</v>
+        <v>-2.66720288788067</v>
       </c>
       <c r="F65" t="n">
-        <v>-2.70160694088892</v>
+        <v>-2.17361048233706</v>
       </c>
       <c r="G65" t="n">
-        <v>1.91818142237362</v>
+        <v>1.86804946221242</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>-1.20333068287382</v>
+        <v>-1.09238905688689</v>
       </c>
       <c r="B66" t="n">
-        <v>-0.914676873356934</v>
+        <v>-0.927718185328618</v>
       </c>
       <c r="C66" t="n">
-        <v>1.47788917882483</v>
+        <v>1.00110893877201</v>
       </c>
       <c r="D66" t="n">
-        <v>1.70174442338726</v>
+        <v>1.16464954214562</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.05764502637678</v>
+        <v>-1.32941284322456</v>
       </c>
       <c r="F66" t="n">
-        <v>-1.28233616387882</v>
+        <v>-1.36842346155781</v>
       </c>
       <c r="G66" t="n">
-        <v>2.03472151201534</v>
+        <v>1.91501666412695</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>-1.47013520884805</v>
+        <v>-1.61267217169178</v>
       </c>
       <c r="B67" t="n">
-        <v>-1.38293530854655</v>
+        <v>-0.896825208587371</v>
       </c>
       <c r="C67" t="n">
-        <v>1.91428571078961</v>
+        <v>1.018155942723</v>
       </c>
       <c r="D67" t="n">
-        <v>2.06041634719811</v>
+        <v>2.02763041849971</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.800229276714997</v>
+        <v>-0.929020761401561</v>
       </c>
       <c r="F67" t="n">
-        <v>-1.91351774500529</v>
+        <v>-0.788359718683696</v>
       </c>
       <c r="G67" t="n">
-        <v>1.97236336550043</v>
+        <v>1.9956607815671</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>-1.03886677767868</v>
+        <v>-1.15073643457901</v>
       </c>
       <c r="B68" t="n">
-        <v>-1.1551095299098</v>
+        <v>-1.09727486108763</v>
       </c>
       <c r="C68" t="n">
-        <v>1.55172979507096</v>
+        <v>1.02143618574739</v>
       </c>
       <c r="D68" t="n">
-        <v>1.37623807251424</v>
+        <v>1.07139185526338</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.09300968545856</v>
+        <v>-1.45778524647645</v>
       </c>
       <c r="F68" t="n">
-        <v>-1.72062336959582</v>
+        <v>-1.23957187652464</v>
       </c>
       <c r="G68" t="n">
-        <v>2.00857289982619</v>
+        <v>1.86974218979049</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>-1.18774834045796</v>
+        <v>-1.2838999214838</v>
       </c>
       <c r="B69" t="n">
-        <v>-0.992290746102664</v>
+        <v>-1.15588945090233</v>
       </c>
       <c r="C69" t="n">
-        <v>1.47283386159179</v>
+        <v>0.875692529888785</v>
       </c>
       <c r="D69" t="n">
-        <v>1.35396244096119</v>
+        <v>1.72418740808916</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.958654508972587</v>
+        <v>-0.854048442814697</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.26161648518994</v>
+        <v>-1.32143471429198</v>
       </c>
       <c r="G69" t="n">
-        <v>2.02700212380425</v>
+        <v>1.97667008029006</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>-1.17042429743512</v>
+        <v>-0.786913363945603</v>
       </c>
       <c r="B70" t="n">
-        <v>-0.987122351705407</v>
+        <v>-1.12919067728532</v>
       </c>
       <c r="C70" t="n">
-        <v>1.65415859941265</v>
+        <v>1.07655149866965</v>
       </c>
       <c r="D70" t="n">
-        <v>1.56418045917812</v>
+        <v>0.845142611176839</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.595006872481776</v>
+        <v>-1.75637025801639</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.4647678033809</v>
+        <v>-1.94451132700561</v>
       </c>
       <c r="G70" t="n">
-        <v>2.02690127629524</v>
+        <v>1.99542681163196</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>-1.18944765761923</v>
+        <v>-1.17057397947643</v>
       </c>
       <c r="B71" t="n">
-        <v>-1.04227567122251</v>
+        <v>-1.13297388813523</v>
       </c>
       <c r="C71" t="n">
-        <v>1.71401989530219</v>
+        <v>1.33439543165095</v>
       </c>
       <c r="D71" t="n">
-        <v>1.40440409327992</v>
+        <v>0.877255337124093</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.984650468358615</v>
+        <v>-0.96422757784904</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.18593436308739</v>
+        <v>-1.97562378171607</v>
       </c>
       <c r="G71" t="n">
-        <v>2.03064071721262</v>
+        <v>1.92527547149841</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>-1.12948518517859</v>
+        <v>-0.896759494902665</v>
       </c>
       <c r="B72" t="n">
-        <v>-1.13448267759239</v>
+        <v>-1.01967789668586</v>
       </c>
       <c r="C72" t="n">
-        <v>1.72191382167978</v>
+        <v>1.02380348880175</v>
       </c>
       <c r="D72" t="n">
-        <v>1.27704803591868</v>
+        <v>0.666268374445888</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.760280844483341</v>
+        <v>-1.3359325070305</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.20172667439212</v>
+        <v>-2.2793765556345</v>
       </c>
       <c r="G72" t="n">
-        <v>2.02948946347988</v>
+        <v>1.94858309295269</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>-1.24238055684942</v>
+        <v>-1.06815062710983</v>
       </c>
       <c r="B73" t="n">
-        <v>-0.999965077648463</v>
+        <v>-1.53523373444227</v>
       </c>
       <c r="C73" t="n">
-        <v>1.40676589572994</v>
+        <v>1.50281266726839</v>
       </c>
       <c r="D73" t="n">
-        <v>1.43273551730104</v>
+        <v>0.980980236075349</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.10180064515501</v>
+        <v>-1.04574550535643</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.95401128214498</v>
+        <v>-1.37528090425929</v>
       </c>
       <c r="G73" t="n">
-        <v>1.9388995904753</v>
+        <v>1.93054850503476</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>-0.879482511405457</v>
+        <v>-0.893237918327675</v>
       </c>
       <c r="B74" t="n">
-        <v>-0.670970981295908</v>
+        <v>-0.915403915310941</v>
       </c>
       <c r="C74" t="n">
-        <v>1.40482089710445</v>
+        <v>1.12518243634312</v>
       </c>
       <c r="D74" t="n">
-        <v>0.748003797649063</v>
+        <v>0.594617489995729</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.46179717732274</v>
+        <v>-1.09210897468767</v>
       </c>
       <c r="F74" t="n">
-        <v>-2.69156163697368</v>
+        <v>-1.38779672183804</v>
       </c>
       <c r="G74" t="n">
-        <v>2.07209314797532</v>
+        <v>2.07205224399865</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>-0.977563532079473</v>
+        <v>-1.1600070393692</v>
       </c>
       <c r="B75" t="n">
-        <v>-0.967469255946267</v>
+        <v>-0.87180249707389</v>
       </c>
       <c r="C75" t="n">
-        <v>1.33842237798604</v>
+        <v>0.883584024211846</v>
       </c>
       <c r="D75" t="n">
-        <v>1.52050452914232</v>
+        <v>1.11572090632155</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.31560708141766</v>
+        <v>-0.932816103012305</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.83306934455607</v>
+        <v>-1.17727775271348</v>
       </c>
       <c r="G75" t="n">
-        <v>1.98170532047757</v>
+        <v>1.98786097825218</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>-1.30331104221695</v>
+        <v>-0.792327710006202</v>
       </c>
       <c r="B76" t="n">
-        <v>-0.871552086770241</v>
+        <v>-0.993742269096783</v>
       </c>
       <c r="C76" t="n">
-        <v>1.37197625948331</v>
+        <v>0.885542119742166</v>
       </c>
       <c r="D76" t="n">
-        <v>1.8159189626892</v>
+        <v>0.409426390530395</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.928578151906871</v>
+        <v>-1.46089612495527</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.17491198029633</v>
+        <v>-2.40222799778635</v>
       </c>
       <c r="G76" t="n">
-        <v>1.95332720069625</v>
+        <v>1.94051981964269</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>-1.36788678370358</v>
+        <v>-0.963965516062066</v>
       </c>
       <c r="B77" t="n">
-        <v>-1.19689162663459</v>
+        <v>-0.888293787274118</v>
       </c>
       <c r="C77" t="n">
-        <v>1.86359478242934</v>
+        <v>1.1102257165159</v>
       </c>
       <c r="D77" t="n">
-        <v>1.81465829761413</v>
+        <v>0.857769942052253</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.764272505092918</v>
+        <v>-1.42535885248367</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.900987057299463</v>
+        <v>-1.61133408914493</v>
       </c>
       <c r="G77" t="n">
-        <v>2.07237204858993</v>
+        <v>2.13427638299536</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>-1.23085342622867</v>
+        <v>-0.749992424293227</v>
       </c>
       <c r="B78" t="n">
-        <v>-1.16072359434281</v>
+        <v>-0.749606926753338</v>
       </c>
       <c r="C78" t="n">
-        <v>2.0817942750416</v>
+        <v>0.765314297108612</v>
       </c>
       <c r="D78" t="n">
-        <v>1.54973592134263</v>
+        <v>0.480490266555727</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.87249534032754</v>
+        <v>-1.67386873586949</v>
       </c>
       <c r="F78" t="n">
-        <v>-2.22140789979472</v>
+        <v>-2.7700430793474</v>
       </c>
       <c r="G78" t="n">
-        <v>2.06641177281511</v>
+        <v>2.07386350410489</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>-1.20955981708503</v>
+        <v>-0.885160619006925</v>
       </c>
       <c r="B79" t="n">
-        <v>-1.19350782116238</v>
+        <v>-1.07043944357067</v>
       </c>
       <c r="C79" t="n">
-        <v>1.71874508815119</v>
+        <v>1.25477873934386</v>
       </c>
       <c r="D79" t="n">
-        <v>1.94632702778359</v>
+        <v>0.867078119171131</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.44001507334293</v>
+        <v>-1.79670845234324</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.46151368782192</v>
+        <v>-1.62978044716512</v>
       </c>
       <c r="G79" t="n">
-        <v>2.05698693776114</v>
+        <v>1.90333295770019</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>-1.34925348133027</v>
+        <v>-1.16841959472063</v>
       </c>
       <c r="B80" t="n">
-        <v>-1.11020307689473</v>
+        <v>-0.906057867017388</v>
       </c>
       <c r="C80" t="n">
-        <v>1.75170503653492</v>
+        <v>0.935903796544753</v>
       </c>
       <c r="D80" t="n">
-        <v>1.90473659071652</v>
+        <v>1.22885409228215</v>
       </c>
       <c r="E80" t="n">
-        <v>-1.2838328508087</v>
+        <v>-1.06701322641953</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.08742692288812</v>
+        <v>-2.13421938494821</v>
       </c>
       <c r="G80" t="n">
-        <v>1.96525709564127</v>
+        <v>2.16251982831671</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>-1.08722104481103</v>
+        <v>-1.04572838901436</v>
       </c>
       <c r="B81" t="n">
-        <v>-0.891103055313651</v>
+        <v>-0.833801201271262</v>
       </c>
       <c r="C81" t="n">
-        <v>1.4167001222567</v>
+        <v>0.860655779635531</v>
       </c>
       <c r="D81" t="n">
-        <v>1.33523253254967</v>
+        <v>1.06721001060237</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.855754008008157</v>
+        <v>-1.25140531174848</v>
       </c>
       <c r="F81" t="n">
-        <v>-1.45897623918444</v>
+        <v>-2.39730640287319</v>
       </c>
       <c r="G81" t="n">
-        <v>2.0412877000386</v>
+        <v>1.9337360758117</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>-1.02725744937271</v>
+        <v>-1.12862950281111</v>
       </c>
       <c r="B82" t="n">
-        <v>-0.920438758592641</v>
+        <v>-0.899434669333077</v>
       </c>
       <c r="C82" t="n">
-        <v>1.50312885999453</v>
+        <v>0.929061940020812</v>
       </c>
       <c r="D82" t="n">
-        <v>1.42877475901655</v>
+        <v>1.24411374002058</v>
       </c>
       <c r="E82" t="n">
-        <v>-1.03121189051935</v>
+        <v>-1.43526845387133</v>
       </c>
       <c r="F82" t="n">
-        <v>-1.52489741698251</v>
+        <v>-1.31950516250741</v>
       </c>
       <c r="G82" t="n">
-        <v>1.98587765909735</v>
+        <v>2.07875526604528</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>-1.05964652094375</v>
+        <v>-1.2059139577001</v>
       </c>
       <c r="B83" t="n">
-        <v>-1.01705913707309</v>
+        <v>-0.794036479180343</v>
       </c>
       <c r="C83" t="n">
-        <v>1.88311009297478</v>
+        <v>0.76926788991986</v>
       </c>
       <c r="D83" t="n">
-        <v>1.26100841291095</v>
+        <v>1.28989153095672</v>
       </c>
       <c r="E83" t="n">
-        <v>-1.09222638195919</v>
+        <v>-0.810641184857512</v>
       </c>
       <c r="F83" t="n">
-        <v>-2.17890946943732</v>
+        <v>-1.12153465484841</v>
       </c>
       <c r="G83" t="n">
-        <v>2.08012412491151</v>
+        <v>1.99281417122525</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>-1.0835206293641</v>
+        <v>-1.507333879548</v>
       </c>
       <c r="B84" t="n">
-        <v>-1.15608174959365</v>
+        <v>-1.30755607769084</v>
       </c>
       <c r="C84" t="n">
-        <v>1.7514642724054</v>
+        <v>1.27449079467438</v>
       </c>
       <c r="D84" t="n">
-        <v>1.04534597546501</v>
+        <v>1.81931250585554</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.772544691086101</v>
+        <v>-0.802822002935038</v>
       </c>
       <c r="F84" t="n">
-        <v>-1.11055883166255</v>
+        <v>-1.7578310393379</v>
       </c>
       <c r="G84" t="n">
-        <v>1.93475431861606</v>
+        <v>1.96416896052392</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>-1.03598933635441</v>
+        <v>-1.02718608355558</v>
       </c>
       <c r="B85" t="n">
-        <v>-1.10517151236037</v>
+        <v>-1.28053521437259</v>
       </c>
       <c r="C85" t="n">
-        <v>1.73846715715532</v>
+        <v>1.29164438001474</v>
       </c>
       <c r="D85" t="n">
-        <v>1.25373259557418</v>
+        <v>0.740080145250098</v>
       </c>
       <c r="E85" t="n">
-        <v>-1.00952358130872</v>
+        <v>-1.25941596574896</v>
       </c>
       <c r="F85" t="n">
-        <v>-1.40640604220573</v>
+        <v>-1.25579731501034</v>
       </c>
       <c r="G85" t="n">
-        <v>2.02135782791266</v>
+        <v>1.95306760922635</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>-0.963121735673645</v>
+        <v>-1.24794043947914</v>
       </c>
       <c r="B86" t="n">
-        <v>-1.12590335662254</v>
+        <v>-0.97756447065912</v>
       </c>
       <c r="C86" t="n">
-        <v>1.52314710326487</v>
+        <v>0.918040557678395</v>
       </c>
       <c r="D86" t="n">
-        <v>1.22658046058934</v>
+        <v>1.31361150929743</v>
       </c>
       <c r="E86" t="n">
-        <v>-1.29922748204429</v>
+        <v>-0.947648464940287</v>
       </c>
       <c r="F86" t="n">
-        <v>-2.63630335754514</v>
+        <v>-1.12087217344447</v>
       </c>
       <c r="G86" t="n">
-        <v>1.95482893584737</v>
+        <v>1.97752307445228</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>-0.914710028563378</v>
+        <v>-0.834321027135032</v>
       </c>
       <c r="B87" t="n">
-        <v>-0.842783808617383</v>
+        <v>-0.966964526106219</v>
       </c>
       <c r="C87" t="n">
-        <v>1.33436231183175</v>
+        <v>0.969741539207844</v>
       </c>
       <c r="D87" t="n">
-        <v>1.07331097391421</v>
+        <v>0.753994963046098</v>
       </c>
       <c r="E87" t="n">
-        <v>-1.24822195196511</v>
+        <v>-1.88594301726992</v>
       </c>
       <c r="F87" t="n">
-        <v>-1.66015177783504</v>
+        <v>-1.78461738516944</v>
       </c>
       <c r="G87" t="n">
-        <v>2.21209226064393</v>
+        <v>1.99722721050532</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>-0.96387094626143</v>
+        <v>-1.1242445766204</v>
       </c>
       <c r="B88" t="n">
-        <v>-0.955550521252458</v>
+        <v>-0.69725439342649</v>
       </c>
       <c r="C88" t="n">
-        <v>1.32556438934389</v>
+        <v>0.620782520006859</v>
       </c>
       <c r="D88" t="n">
-        <v>1.28540512873698</v>
+        <v>1.17773949435892</v>
       </c>
       <c r="E88" t="n">
-        <v>-1.04089554180896</v>
+        <v>-1.76190841589118</v>
       </c>
       <c r="F88" t="n">
-        <v>-1.56847515889614</v>
+        <v>-1.35670537010617</v>
       </c>
       <c r="G88" t="n">
-        <v>2.10712359855964</v>
+        <v>1.99570535052531</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>-1.03216404165702</v>
+        <v>-0.963358386192332</v>
       </c>
       <c r="B89" t="n">
-        <v>-0.757895684678806</v>
+        <v>-0.988955418947146</v>
       </c>
       <c r="C89" t="n">
-        <v>1.35933879329246</v>
+        <v>0.946101632892214</v>
       </c>
       <c r="D89" t="n">
-        <v>1.31369713646199</v>
+        <v>0.804748035850498</v>
       </c>
       <c r="E89" t="n">
-        <v>-1.23966002600722</v>
+        <v>-1.29610694142982</v>
       </c>
       <c r="F89" t="n">
-        <v>-2.36827093062699</v>
+        <v>-2.33692293616569</v>
       </c>
       <c r="G89" t="n">
-        <v>2.00723383249111</v>
+        <v>1.99777061066714</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>-1.14638866205216</v>
+        <v>-0.842582223801749</v>
       </c>
       <c r="B90" t="n">
-        <v>-1.29714311610965</v>
+        <v>-0.918459848558428</v>
       </c>
       <c r="C90" t="n">
-        <v>2.05928296426596</v>
+        <v>1.02146107836757</v>
       </c>
       <c r="D90" t="n">
-        <v>1.25204228812383</v>
+        <v>0.731092770780753</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.893551886140443</v>
+        <v>-1.6438345130963</v>
       </c>
       <c r="F90" t="n">
-        <v>-1.08976813754661</v>
+        <v>-1.64163159272632</v>
       </c>
       <c r="G90" t="n">
-        <v>2.06558667796697</v>
+        <v>2.09380341467972</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>-0.813267617937397</v>
+        <v>-1.37575150122109</v>
       </c>
       <c r="B91" t="n">
-        <v>-1.14196526430773</v>
+        <v>-0.851376188785728</v>
       </c>
       <c r="C91" t="n">
-        <v>1.56385056708869</v>
+        <v>0.967689171259785</v>
       </c>
       <c r="D91" t="n">
-        <v>0.815789207607693</v>
+        <v>1.71952833751908</v>
       </c>
       <c r="E91" t="n">
-        <v>-1.32675744702281</v>
+        <v>-0.840645781854385</v>
       </c>
       <c r="F91" t="n">
-        <v>-1.66292326040703</v>
+        <v>-1.05184661821694</v>
       </c>
       <c r="G91" t="n">
-        <v>1.9797996813289</v>
+        <v>2.02813518995722</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>-1.33346252154412</v>
+        <v>-1.25587792211644</v>
       </c>
       <c r="B92" t="n">
-        <v>-0.915015506338318</v>
+        <v>-0.77929341065267</v>
       </c>
       <c r="C92" t="n">
-        <v>1.4449270391358</v>
+        <v>0.86768467523787</v>
       </c>
       <c r="D92" t="n">
-        <v>1.68820416269252</v>
+        <v>1.76969588466668</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.972888167197347</v>
+        <v>-1.38579374800332</v>
       </c>
       <c r="F92" t="n">
-        <v>-1.86001319673549</v>
+        <v>-1.32227669161255</v>
       </c>
       <c r="G92" t="n">
-        <v>2.02687259673752</v>
+        <v>2.01623699193624</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>-0.799619802191013</v>
+        <v>-1.43631570843019</v>
       </c>
       <c r="B93" t="n">
-        <v>-0.800352626691041</v>
+        <v>-1.02617148368983</v>
       </c>
       <c r="C93" t="n">
-        <v>1.34279978804444</v>
+        <v>1.30065978929157</v>
       </c>
       <c r="D93" t="n">
-        <v>0.674760940070484</v>
+        <v>1.41336056571511</v>
       </c>
       <c r="E93" t="n">
-        <v>-1.55528976725481</v>
+        <v>-0.566161731368066</v>
       </c>
       <c r="F93" t="n">
-        <v>-2.45243185331669</v>
+        <v>-1.54609192363949</v>
       </c>
       <c r="G93" t="n">
-        <v>1.96404643257778</v>
+        <v>2.03469907609242</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>-1.29108297120253</v>
+        <v>-0.976262534436638</v>
       </c>
       <c r="B94" t="n">
-        <v>-0.966308651373671</v>
+        <v>-0.971908235783815</v>
       </c>
       <c r="C94" t="n">
-        <v>1.50871874323804</v>
+        <v>1.12066026876088</v>
       </c>
       <c r="D94" t="n">
-        <v>1.34854182894566</v>
+        <v>0.905411331626438</v>
       </c>
       <c r="E94" t="n">
-        <v>-1.09399192072421</v>
+        <v>-1.18546015698376</v>
       </c>
       <c r="F94" t="n">
-        <v>-1.00938777842919</v>
+        <v>-1.55130244237742</v>
       </c>
       <c r="G94" t="n">
-        <v>2.05047103484497</v>
+        <v>2.03164132892882</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>-1.01429635068568</v>
+        <v>-1.30350425660569</v>
       </c>
       <c r="B95" t="n">
-        <v>-0.923317255770461</v>
+        <v>-0.916970277991993</v>
       </c>
       <c r="C95" t="n">
-        <v>1.48141604901068</v>
+        <v>0.860136425882743</v>
       </c>
       <c r="D95" t="n">
-        <v>1.17627788234253</v>
+        <v>1.53416318270948</v>
       </c>
       <c r="E95" t="n">
-        <v>-1.12233164730945</v>
+        <v>-1.16506502821393</v>
       </c>
       <c r="F95" t="n">
-        <v>-1.51613519920672</v>
+        <v>-2.25317549002801</v>
       </c>
       <c r="G95" t="n">
-        <v>1.91842237716624</v>
+        <v>1.9510131992059</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>-0.52058610354173</v>
+        <v>-0.889437649890655</v>
       </c>
       <c r="B96" t="n">
-        <v>-1.01160148200157</v>
+        <v>-0.868467368128155</v>
       </c>
       <c r="C96" t="n">
-        <v>1.57344591078248</v>
+        <v>0.858924556442055</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.109296285302844</v>
+        <v>0.835419938458171</v>
       </c>
       <c r="E96" t="n">
-        <v>-1.36940606330467</v>
+        <v>-1.67568056767289</v>
       </c>
       <c r="F96" t="n">
-        <v>-1.7714132414587</v>
+        <v>-1.69206887080828</v>
       </c>
       <c r="G96" t="n">
-        <v>1.99897155419487</v>
+        <v>1.99956869272755</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>-0.764184748192094</v>
+        <v>-1.18096514277988</v>
       </c>
       <c r="B97" t="n">
-        <v>-1.0962890924418</v>
+        <v>-1.01330180225652</v>
       </c>
       <c r="C97" t="n">
-        <v>1.4939632789186</v>
+        <v>1.03002143932886</v>
       </c>
       <c r="D97" t="n">
-        <v>1.01949066791309</v>
+        <v>0.985341110293004</v>
       </c>
       <c r="E97" t="n">
-        <v>-1.74298930255111</v>
+        <v>-1.2351369145125</v>
       </c>
       <c r="F97" t="n">
-        <v>-2.83137235141517</v>
+        <v>-1.12761855399113</v>
       </c>
       <c r="G97" t="n">
-        <v>2.02195276193096</v>
+        <v>1.98467357058719</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>-1.42552130660447</v>
+        <v>-1.07370013516992</v>
       </c>
       <c r="B98" t="n">
-        <v>-1.35259188185259</v>
+        <v>-0.682326408811179</v>
       </c>
       <c r="C98" t="n">
-        <v>1.88631525358677</v>
+        <v>0.713454517805307</v>
       </c>
       <c r="D98" t="n">
-        <v>1.90741341086832</v>
+        <v>0.922362221640183</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.618320618087327</v>
+        <v>-1.65827193967847</v>
       </c>
       <c r="F98" t="n">
-        <v>-1.66614102796291</v>
+        <v>-1.25250291093018</v>
       </c>
       <c r="G98" t="n">
-        <v>1.97113062554391</v>
+        <v>1.96580201866522</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>-0.775241889893614</v>
+        <v>-1.00581876751928</v>
       </c>
       <c r="B99" t="n">
-        <v>-1.12116297327627</v>
+        <v>-1.01156869052866</v>
       </c>
       <c r="C99" t="n">
-        <v>1.63849483688066</v>
+        <v>1.15044820789036</v>
       </c>
       <c r="D99" t="n">
-        <v>0.508483026608825</v>
+        <v>0.937737635383039</v>
       </c>
       <c r="E99" t="n">
-        <v>-1.37065607235343</v>
+        <v>-1.27429609452575</v>
       </c>
       <c r="F99" t="n">
-        <v>-2.36584694570459</v>
+        <v>-2.325229907128</v>
       </c>
       <c r="G99" t="n">
-        <v>1.97923370636941</v>
+        <v>1.9869371901552</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>-1.43344170605083</v>
+        <v>-0.93164878629187</v>
       </c>
       <c r="B100" t="n">
-        <v>-0.905009649817633</v>
+        <v>-0.736004462109011</v>
       </c>
       <c r="C100" t="n">
-        <v>1.42283597403205</v>
+        <v>0.706645705013766</v>
       </c>
       <c r="D100" t="n">
-        <v>1.89981117833047</v>
+        <v>0.979512155750759</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.76091595284533</v>
+        <v>-1.85490847789631</v>
       </c>
       <c r="F100" t="n">
-        <v>-0.849061781188195</v>
+        <v>-1.6454671693496</v>
       </c>
       <c r="G100" t="n">
-        <v>2.14201178453293</v>
+        <v>1.98227174818761</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>-1.26810413646163</v>
+        <v>-0.835402303766262</v>
       </c>
       <c r="B101" t="n">
-        <v>-0.871968951926678</v>
+        <v>-1.45613799626674</v>
       </c>
       <c r="C101" t="n">
-        <v>1.38353640682113</v>
+        <v>1.60204423979432</v>
       </c>
       <c r="D101" t="n">
-        <v>1.78297444069878</v>
+        <v>0.45293529099645</v>
       </c>
       <c r="E101" t="n">
-        <v>-1.61154652988088</v>
+        <v>-1.49232475299524</v>
       </c>
       <c r="F101" t="n">
-        <v>-1.43138071044994</v>
+        <v>-2.30153149946249</v>
       </c>
       <c r="G101" t="n">
-        <v>1.93581407223412</v>
+        <v>1.71129520503187</v>
       </c>
     </row>
   </sheetData>
@@ -3146,826 +3149,826 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.248907542450121</v>
+        <v>4.97338553044861</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0806782880539029</v>
+        <v>0.299082457700549</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1.07040214133927</v>
+        <v>0.408495580401005</v>
       </c>
       <c r="B3" t="n">
-        <v>0.180334659878328</v>
+        <v>0.219572709685491</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2.65136643723644</v>
+        <v>0.633034116269982</v>
       </c>
       <c r="B4" t="n">
-        <v>0.361245775467258</v>
+        <v>0.236157127027264</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.113254090861241</v>
+        <v>0.791790199252031</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0363207771844901</v>
+        <v>0.226369224805046</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>19.3171323599872</v>
+        <v>0.315375782320105</v>
       </c>
       <c r="B6" t="n">
-        <v>0.408671396107832</v>
+        <v>0.146442054509944</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.276881362191013</v>
+        <v>0.32108235009429</v>
       </c>
       <c r="B7" t="n">
-        <v>0.243340070856405</v>
+        <v>0.083973543583732</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124.024213439731</v>
+        <v>54.7241149017962</v>
       </c>
       <c r="B8" t="n">
-        <v>0.558367196756747</v>
+        <v>0.485335490972998</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1.12676577482454</v>
+        <v>2.34126031946298</v>
       </c>
       <c r="B9" t="n">
-        <v>0.30798329496166</v>
+        <v>0.224932583195376</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.449074181481472</v>
+        <v>0.539251888035315</v>
       </c>
       <c r="B10" t="n">
-        <v>0.515472260309176</v>
+        <v>0.123136788960957</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.491651576070679</v>
+        <v>12.0355090267081</v>
       </c>
       <c r="B11" t="n">
-        <v>0.218426071250487</v>
+        <v>0.368822279472269</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.518028997734039</v>
+        <v>11.1598838459724</v>
       </c>
       <c r="B12" t="n">
-        <v>0.270076953245681</v>
+        <v>0.421496456198229</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3.17459314398379</v>
+        <v>29.7018419557438</v>
       </c>
       <c r="B13" t="n">
-        <v>0.256433802033631</v>
+        <v>0.428525376814278</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>240.998747453651</v>
+        <v>0.377336357734481</v>
       </c>
       <c r="B14" t="n">
-        <v>0.635775647100509</v>
+        <v>0.395102193476232</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.850322985825786</v>
+        <v>233.764157642349</v>
       </c>
       <c r="B15" t="n">
-        <v>0.146751009312577</v>
+        <v>0.5782980745006</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.211542513899446</v>
+        <v>3.81086211957332</v>
       </c>
       <c r="B16" t="n">
-        <v>0.102503766928934</v>
+        <v>0.283313641813473</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>336.312054847586</v>
+        <v>8.93574053488654</v>
       </c>
       <c r="B17" t="n">
-        <v>0.655089524878236</v>
+        <v>0.349737989857736</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>26.7609217829284</v>
+        <v>4.31138746301307</v>
       </c>
       <c r="B18" t="n">
-        <v>0.425426402651336</v>
+        <v>0.284932520172965</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3.2456686081293</v>
+        <v>0.15918903926374</v>
       </c>
       <c r="B19" t="n">
-        <v>0.277490006183597</v>
+        <v>0.0875650847856462</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>21.429864864002</v>
+        <v>7.15285745933938</v>
       </c>
       <c r="B20" t="n">
-        <v>0.453954505356984</v>
+        <v>0.333347752545766</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>6.92955162746538</v>
+        <v>51.7735965188644</v>
       </c>
       <c r="B21" t="n">
-        <v>0.309721231831303</v>
+        <v>0.476294099651285</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>9.46533702016284</v>
+        <v>9.07781336203471</v>
       </c>
       <c r="B22" t="n">
-        <v>0.44500973991102</v>
+        <v>0.342055579082945</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.603313271724276</v>
+        <v>139.082640181121</v>
       </c>
       <c r="B23" t="n">
-        <v>0.257937786189242</v>
+        <v>0.547958084007659</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3.43237565288166</v>
+        <v>4.82283973390813</v>
       </c>
       <c r="B24" t="n">
-        <v>0.269579089206499</v>
+        <v>0.291201529635215</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2.15686698131951</v>
+        <v>3.76424764902995</v>
       </c>
       <c r="B25" t="n">
-        <v>0.366969663800479</v>
+        <v>0.271668845689995</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>22.9603733030952</v>
+        <v>10.9602083358765</v>
       </c>
       <c r="B26" t="n">
-        <v>0.479214242519763</v>
+        <v>0.357461371967771</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>4.37171512029678</v>
+        <v>2.3360868079477</v>
       </c>
       <c r="B27" t="n">
-        <v>0.283439871487435</v>
+        <v>0.246151209314791</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.583040060089285</v>
+        <v>1.40581124543565</v>
       </c>
       <c r="B28" t="n">
-        <v>0.427860425217489</v>
+        <v>0.194443887722717</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>144.754568135442</v>
+        <v>1.78658815570985</v>
       </c>
       <c r="B29" t="n">
-        <v>0.602088812753161</v>
+        <v>0.21213236586645</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>28.1535706157586</v>
+        <v>0.238629585815583</v>
       </c>
       <c r="B30" t="n">
-        <v>0.425238056040459</v>
+        <v>0.0741848937173714</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>47.4052413567375</v>
+        <v>5.26086194604966</v>
       </c>
       <c r="B31" t="n">
-        <v>0.46192411524837</v>
+        <v>0.304076829461697</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.484507334489687</v>
+        <v>13.9232227500464</v>
       </c>
       <c r="B32" t="n">
-        <v>0.269123023564203</v>
+        <v>0.369319863797884</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>5.18412177435529</v>
+        <v>0.567927410990392</v>
       </c>
       <c r="B33" t="n">
-        <v>0.292683268283778</v>
+        <v>0.12988526868559</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.270410989932054</v>
+        <v>0.420208860547441</v>
       </c>
       <c r="B34" t="n">
-        <v>0.176267475996415</v>
+        <v>0.218861907349146</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>6.53160651188545</v>
+        <v>29.9472197003907</v>
       </c>
       <c r="B35" t="n">
-        <v>0.310429803112707</v>
+        <v>0.462916778103871</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.938504465882225</v>
+        <v>0.749262280474304</v>
       </c>
       <c r="B36" t="n">
-        <v>0.284049026788089</v>
+        <v>0.138284314389689</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>11.9951894405834</v>
+        <v>3.99862626407479</v>
       </c>
       <c r="B37" t="n">
-        <v>0.371678261431368</v>
+        <v>0.274686586161956</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.383376575407425</v>
+        <v>400.519547827959</v>
       </c>
       <c r="B38" t="n">
-        <v>0.266617546194662</v>
+        <v>0.63295756557005</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3.21898927856491</v>
+        <v>0.344489848108558</v>
       </c>
       <c r="B39" t="n">
-        <v>0.350914517117101</v>
+        <v>0.348527918734833</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.156569126709535</v>
+        <v>234.323437432342</v>
       </c>
       <c r="B40" t="n">
-        <v>0.0780224983498665</v>
+        <v>0.578313367047031</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.289785107084952</v>
+        <v>3.72608283819351</v>
       </c>
       <c r="B41" t="n">
-        <v>0.234978860825451</v>
+        <v>0.271251777114197</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>7.45499375928705</v>
+        <v>253.969307278675</v>
       </c>
       <c r="B42" t="n">
-        <v>0.327952769997709</v>
+        <v>0.59021990562815</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1.91166924062492</v>
+        <v>0.281926266831153</v>
       </c>
       <c r="B43" t="n">
-        <v>0.224189647168394</v>
+        <v>0.194048461733665</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.734349274427232</v>
+        <v>0.960888250016428</v>
       </c>
       <c r="B44" t="n">
-        <v>0.227297658323506</v>
+        <v>0.347727881999357</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2.03645718732475</v>
+        <v>0.75709013308416</v>
       </c>
       <c r="B45" t="n">
-        <v>0.370683998720861</v>
+        <v>0.146943788166268</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>10.8154453855081</v>
+        <v>2.88562848205829</v>
       </c>
       <c r="B46" t="n">
-        <v>0.360174880042432</v>
+        <v>0.361438522005922</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.556107544882406</v>
+        <v>15.5002226461473</v>
       </c>
       <c r="B47" t="n">
-        <v>0.126643808947003</v>
+        <v>0.38663187726261</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>8.48722356718016</v>
+        <v>6.35294368447765</v>
       </c>
       <c r="B48" t="n">
-        <v>0.345683838671563</v>
+        <v>0.32161592673049</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.403878431207826</v>
+        <v>5.14034461548674</v>
       </c>
       <c r="B49" t="n">
-        <v>0.260511853865896</v>
+        <v>0.397210175192907</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>30.6798064323094</v>
+        <v>4.88686163787517</v>
       </c>
       <c r="B50" t="n">
-        <v>0.43898086985314</v>
+        <v>0.295552396410747</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>12.3413021989979</v>
+        <v>0.293225123257215</v>
       </c>
       <c r="B51" t="n">
-        <v>0.356675982383662</v>
+        <v>0.166237176923074</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>14.7638227488808</v>
+        <v>3.47217285984319</v>
       </c>
       <c r="B52" t="n">
-        <v>0.38063126298528</v>
+        <v>0.367350134214983</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>16.9498915565319</v>
+        <v>222.941420453421</v>
       </c>
       <c r="B53" t="n">
-        <v>0.469479378154062</v>
+        <v>0.567876825395035</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.72353818154587</v>
+        <v>7.94664218533977</v>
       </c>
       <c r="B54" t="n">
-        <v>0.30638842981378</v>
+        <v>0.336609467095703</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0.743889406389223</v>
+        <v>0.289386332116483</v>
       </c>
       <c r="B55" t="n">
-        <v>0.147813995768323</v>
+        <v>0.0825091892270081</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>9.44491009590241</v>
+        <v>6.62086866062509</v>
       </c>
       <c r="B56" t="n">
-        <v>0.400220742010967</v>
+        <v>0.317413205131039</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>3.49892187224291</v>
+        <v>1.40041481104804</v>
       </c>
       <c r="B57" t="n">
-        <v>0.265080782048326</v>
+        <v>0.197728872021184</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>3.03405450225041</v>
+        <v>7.98446018179189</v>
       </c>
       <c r="B58" t="n">
-        <v>0.463767034814901</v>
+        <v>0.33206971861244</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>3.165445836496</v>
+        <v>149.436953185651</v>
       </c>
       <c r="B59" t="n">
-        <v>0.304106713112839</v>
+        <v>0.579908030679941</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>7.15543617783285</v>
+        <v>6.6430139014188</v>
       </c>
       <c r="B60" t="n">
-        <v>0.325992437313026</v>
+        <v>0.328104875213626</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0.715127188429633</v>
+        <v>2.63659805684808</v>
       </c>
       <c r="B61" t="n">
-        <v>0.292909456573953</v>
+        <v>0.246415941491394</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1.96960231694562</v>
+        <v>41.696636306569</v>
       </c>
       <c r="B62" t="n">
-        <v>0.22795151091732</v>
+        <v>0.492626613111326</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>4.73137036378187</v>
+        <v>19.4400593377529</v>
       </c>
       <c r="B63" t="n">
-        <v>0.294319058519481</v>
+        <v>0.410435373432468</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>9.85266551727779</v>
+        <v>1.87174597614413</v>
       </c>
       <c r="B64" t="n">
-        <v>0.452482449429405</v>
+        <v>0.215594774420643</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>37.9486626005116</v>
+        <v>975.543357214737</v>
       </c>
       <c r="B65" t="n">
-        <v>0.598733782786663</v>
+        <v>0.661705511240434</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>0.780388166208033</v>
+        <v>2.75544077609206</v>
       </c>
       <c r="B66" t="n">
-        <v>0.149954992821286</v>
+        <v>0.244719953959393</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0.33935537635958</v>
+        <v>0.310514911326402</v>
       </c>
       <c r="B67" t="n">
-        <v>0.227701210665708</v>
+        <v>0.465081119061561</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>38.1451993495172</v>
+        <v>0.888697838043038</v>
       </c>
       <c r="B68" t="n">
-        <v>0.438972333086221</v>
+        <v>0.1614646542408</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>0.433447744101818</v>
+        <v>2.11418880722511</v>
       </c>
       <c r="B69" t="n">
-        <v>0.115592992260314</v>
+        <v>0.214404086736406</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>4.74504513333334</v>
+        <v>232.014331193207</v>
       </c>
       <c r="B70" t="n">
-        <v>0.291825506069965</v>
+        <v>0.580055234038132</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>0.251616251897165</v>
+        <v>0.36753353002134</v>
       </c>
       <c r="B71" t="n">
-        <v>0.0794368024254959</v>
+        <v>0.20978277650931</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.32051669433314</v>
+        <v>9.65841731546244</v>
       </c>
       <c r="B72" t="n">
-        <v>0.0887009143241584</v>
+        <v>0.365071805899743</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0.400546667455982</v>
+        <v>2.54078972619089</v>
       </c>
       <c r="B73" t="n">
-        <v>0.220659326690533</v>
+        <v>0.245583197318757</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>145.105712743081</v>
+        <v>4.49878408557788</v>
       </c>
       <c r="B74" t="n">
-        <v>0.556347955884781</v>
+        <v>0.281959928502621</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>87.5370896675238</v>
+        <v>0.190582075865319</v>
       </c>
       <c r="B75" t="n">
-        <v>0.506514962488064</v>
+        <v>0.0516995804153233</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>0.23162713212447</v>
+        <v>10.2053953656598</v>
       </c>
       <c r="B76" t="n">
-        <v>0.0775979068446782</v>
+        <v>0.498328133856598</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0.188574586048354</v>
+        <v>19.5342348738237</v>
       </c>
       <c r="B77" t="n">
-        <v>0.331104711026119</v>
+        <v>0.394031925508202</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>0.461210532175997</v>
+        <v>119.944092849773</v>
       </c>
       <c r="B78" t="n">
-        <v>0.240705501399868</v>
+        <v>0.647072959150503</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>5.00857410194151</v>
+        <v>19.5899887475976</v>
       </c>
       <c r="B79" t="n">
-        <v>0.293846749968496</v>
+        <v>0.410278492730863</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>0.111265469615184</v>
+        <v>0.372256797849504</v>
       </c>
       <c r="B80" t="n">
-        <v>0.111222983261633</v>
+        <v>0.302915973628858</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>3.38052167873002</v>
+        <v>7.73271945103185</v>
       </c>
       <c r="B81" t="n">
-        <v>0.278530427390305</v>
+        <v>0.439948829894893</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>13.6900104247659</v>
+        <v>1.45626865886215</v>
       </c>
       <c r="B82" t="n">
-        <v>0.368806662398239</v>
+        <v>0.191815276854089</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1.3552490558866</v>
+        <v>0.32309925845462</v>
       </c>
       <c r="B83" t="n">
-        <v>0.320430825741732</v>
+        <v>0.116659734802038</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>0.157950928953976</v>
+        <v>0.392764949196271</v>
       </c>
       <c r="B84" t="n">
-        <v>0.0970554979891332</v>
+        <v>0.203452388083389</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>2.84290763400465</v>
+        <v>0.855973862423607</v>
       </c>
       <c r="B85" t="n">
-        <v>0.242339063303787</v>
+        <v>0.156843687690083</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>66.3105051397431</v>
+        <v>0.238120486803534</v>
       </c>
       <c r="B86" t="n">
-        <v>0.484359520173418</v>
+        <v>0.100323503828093</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>33.2270184298224</v>
+        <v>69.2998969950981</v>
       </c>
       <c r="B87" t="n">
-        <v>0.439487972547772</v>
+        <v>0.49670164966495</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>7.74048751951854</v>
+        <v>3.0072303962876</v>
       </c>
       <c r="B88" t="n">
-        <v>0.347617791740702</v>
+        <v>0.260419968077092</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>9.88667304888402</v>
+        <v>7.79929315349426</v>
       </c>
       <c r="B89" t="n">
-        <v>0.387888377522719</v>
+        <v>0.411654688763978</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>0.188390845953411</v>
+        <v>24.8659251735061</v>
       </c>
       <c r="B90" t="n">
-        <v>0.119014647697224</v>
+        <v>0.422221328339239</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>17.9544682517755</v>
+        <v>0.313666818367952</v>
       </c>
       <c r="B91" t="n">
-        <v>0.40906421024802</v>
+        <v>0.151439052881913</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>0.313999920761661</v>
+        <v>1.35079560306199</v>
       </c>
       <c r="B92" t="n">
-        <v>0.193891007220939</v>
+        <v>0.188951510094653</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>104.874291360942</v>
+        <v>0.388851882224519</v>
       </c>
       <c r="B93" t="n">
-        <v>0.4964077208074</v>
+        <v>0.316198765504523</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>0.196238416620125</v>
+        <v>9.32468850059022</v>
       </c>
       <c r="B94" t="n">
-        <v>0.200208979066687</v>
+        <v>0.35076745577849</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>9.06651806455488</v>
+        <v>1.34113524558413</v>
       </c>
       <c r="B95" t="n">
-        <v>0.330723081731003</v>
+        <v>0.272186223006857</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>68.7326206381445</v>
+        <v>24.5220724199769</v>
       </c>
       <c r="B96" t="n">
-        <v>0.4918174342989</v>
+        <v>0.433193578042331</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>306.598423638323</v>
+        <v>0.0924258385975836</v>
       </c>
       <c r="B97" t="n">
-        <v>0.658801421598518</v>
+        <v>0.0839949846246999</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>0.541444910643647</v>
+        <v>0.884629407677194</v>
       </c>
       <c r="B98" t="n">
-        <v>0.286172184264764</v>
+        <v>0.163038931753712</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>20.2377644807599</v>
+        <v>3.19552794677971</v>
       </c>
       <c r="B99" t="n">
-        <v>0.425661124176957</v>
+        <v>0.441753893847199</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>0.316860440854558</v>
+        <v>26.2962635343344</v>
       </c>
       <c r="B100" t="n">
-        <v>0.417047890362063</v>
+        <v>0.429479012137563</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>4.36533424792259</v>
+        <v>12.3516191586551</v>
       </c>
       <c r="B101" t="n">
-        <v>0.283189571170066</v>
+        <v>0.470176136970765</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B103" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>22.2969682793383</v>
+        <v>36.5545629006352</v>
       </c>
       <c r="B104" t="n">
-        <v>0.320754613272768</v>
+        <v>0.318364224586887</v>
       </c>
     </row>
   </sheetData>
@@ -3981,18 +3984,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46016.9923169886</v>
+        <v>46026.2924708093</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
